--- a/employee_surveys/027_office_reopening_survey--employee_surveys.xlsx
+++ b/employee_surveys/027_office_reopening_survey--employee_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -771,7 +771,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>If other, please specify</t>
+          <t>Office Reopening Concerns Other</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -794,7 +794,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>If other, please specify</t>
+          <t>Reopen Frequency Other</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -817,7 +817,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>If other, please specify</t>
+          <t>Reopen Reasons Other</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -840,7 +840,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>If other, please specify</t>
+          <t>Reopen Concerns Other</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -863,7 +863,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>If other, please specify</t>
+          <t>Reopen Date Other</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -881,7 +881,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>office_reopening_frequency</t>
+          <t>office_reopening_frequency_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>reopen_frequency_other</t>
+          <t>reopen_frequency_other_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -950,7 +950,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>reopen_reasons_other</t>
+          <t>reopen_reasons_other_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>If other, please provide details</t>
+          <t>Reopen Frequency Details</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>How often do you expect to visit the office?</t>
+          <t>Reopen Frequency</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>reopen_concerns</t>
+          <t>reopen_concerns_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1121,7 +1121,7 @@
   <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1384,7 +1384,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>office_reopening_frequency_choices</t>
+          <t>office_reopening_frequency_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1401,7 +1401,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>office_reopening_frequency_choices</t>
+          <t>office_reopening_frequency_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1418,7 +1418,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>office_reopening_frequency_choices</t>
+          <t>office_reopening_frequency_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1435,7 +1435,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>office_reopening_frequency_choices</t>
+          <t>office_reopening_frequency_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
